--- a/sales_dash/data/planning/audio_array/ASIN Planning file - Sep 2026.xlsx
+++ b/sales_dash/data/planning/audio_array/ASIN Planning file - Sep 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\Audio Array\Audio Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B94D2F5-ABC3-4619-81E7-7457AD529324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51E7F0B-0D70-4A7B-991D-9942DAFEACEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="573">
   <si>
     <t>ASIN</t>
   </si>
@@ -1687,318 +1687,6 @@
   </si>
   <si>
     <t>AA-28</t>
-  </si>
-  <si>
-    <t>04 channels Mixer</t>
-  </si>
-  <si>
-    <t>06 channels Mixer</t>
-  </si>
-  <si>
-    <t>10 channels mixer</t>
-  </si>
-  <si>
-    <t>12 channels Mixer</t>
-  </si>
-  <si>
-    <t>16 Channel Mixer</t>
-  </si>
-  <si>
-    <t>16 Channel Mixer With Carry Case</t>
-  </si>
-  <si>
-    <t>24 Channel Mixer</t>
-  </si>
-  <si>
-    <t>24 Channel Mixer With Carry Case</t>
-  </si>
-  <si>
-    <t>37 Key Electronic Keyboard Black</t>
-  </si>
-  <si>
-    <t>37 Key Electronic Keyboard White</t>
-  </si>
-  <si>
-    <t>4 channels Mixer</t>
-  </si>
-  <si>
-    <t>4 channels mixer with OTG</t>
-  </si>
-  <si>
-    <t>5" Studio Monitor Speaker</t>
-  </si>
-  <si>
-    <t>6 channels mixer</t>
-  </si>
-  <si>
-    <t>61 Key Electronic Keyboard With LCD DIsplay</t>
-  </si>
-  <si>
-    <t>61 Key Electronic Keyboard With LED DIsplay</t>
-  </si>
-  <si>
-    <t>8 channels Mixer</t>
-  </si>
-  <si>
-    <t>Boom Arm - RGB</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - USB</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - USB - RGB</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - XLR</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit + RGB</t>
-  </si>
-  <si>
-    <t>Condenser Mic with Boom Arm</t>
-  </si>
-  <si>
-    <t>DI box</t>
-  </si>
-  <si>
-    <t>Dual 12" 160W Bluetooth Party Speaker</t>
-  </si>
-  <si>
-    <t>Dual UHF Wireless Microphone With Receiver</t>
-  </si>
-  <si>
-    <t>Dual UHF Wireless Microphone With Receiver Box</t>
-  </si>
-  <si>
-    <t>GB-01</t>
-  </si>
-  <si>
-    <t>GB-02</t>
-  </si>
-  <si>
-    <t>GB-03</t>
-  </si>
-  <si>
-    <t>GB-04</t>
-  </si>
-  <si>
-    <t>GB-05</t>
-  </si>
-  <si>
-    <t>Guitar Transreceiver</t>
-  </si>
-  <si>
-    <t>Hand held Mic</t>
-  </si>
-  <si>
-    <t>Hand held Mic + Boom Arm</t>
-  </si>
-  <si>
-    <t>Hand held Mic + Stand</t>
-  </si>
-  <si>
-    <t>Headphone Splitter</t>
-  </si>
-  <si>
-    <t>IEM With Receiver &amp; Transmitter</t>
-  </si>
-  <si>
-    <t>Instrument Microphone - Drum Kit</t>
-  </si>
-  <si>
-    <t>KB-01</t>
-  </si>
-  <si>
-    <t>Lavalier Microphone</t>
-  </si>
-  <si>
-    <t>Line Mixer</t>
-  </si>
-  <si>
-    <t>Low Profile Boom Arm</t>
-  </si>
-  <si>
-    <t>Mic Activator</t>
-  </si>
-  <si>
-    <t>Microphone Isolation Shield</t>
-  </si>
-  <si>
-    <t>Microphone with Speaker</t>
-  </si>
-  <si>
-    <t>Mobile Microphone</t>
-  </si>
-  <si>
-    <t>Monitor Speaker Stand Pair</t>
-  </si>
-  <si>
-    <t>One Transmitter With One Receiver</t>
-  </si>
-  <si>
-    <t>One Transmitter With One Receiver and Earphone</t>
-  </si>
-  <si>
-    <t>One Transmitter With Two Receiver</t>
-  </si>
-  <si>
-    <t>PB-01</t>
-  </si>
-  <si>
-    <t>PB-02</t>
-  </si>
-  <si>
-    <t>PB-03</t>
-  </si>
-  <si>
-    <t>PB-04</t>
-  </si>
-  <si>
-    <t>PB-05</t>
-  </si>
-  <si>
-    <t>PB-06</t>
-  </si>
-  <si>
-    <t>PB-07</t>
-  </si>
-  <si>
-    <t>PB-08</t>
-  </si>
-  <si>
-    <t>PB-09</t>
-  </si>
-  <si>
-    <t>PB-10</t>
-  </si>
-  <si>
-    <t>PB-11</t>
-  </si>
-  <si>
-    <t>PB-12</t>
-  </si>
-  <si>
-    <t>PB-13</t>
-  </si>
-  <si>
-    <t>PB-14</t>
-  </si>
-  <si>
-    <t>PB-15</t>
-  </si>
-  <si>
-    <t>PB-16</t>
-  </si>
-  <si>
-    <t>PB-17</t>
-  </si>
-  <si>
-    <t>PB-18</t>
-  </si>
-  <si>
-    <t>Portable Speaker with Mic</t>
-  </si>
-  <si>
-    <t>Premium Boom Arm</t>
-  </si>
-  <si>
-    <t>Quad UHF Wireless Microphone With Receiver Box</t>
-  </si>
-  <si>
-    <t>RGB USB Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>Ring Light</t>
-  </si>
-  <si>
-    <t>Single UHF Wireless &amp; Wired Microphone With Receiver</t>
-  </si>
-  <si>
-    <t>Single UHF Wireless Microphone With Receiver</t>
-  </si>
-  <si>
-    <t>Single UHF Wireless Microphone With UHF &amp; USB Receiver</t>
-  </si>
-  <si>
-    <t>Stand</t>
-  </si>
-  <si>
-    <t>Studio Monitor Speaker</t>
-  </si>
-  <si>
-    <t>Tripod</t>
-  </si>
-  <si>
-    <t>Tripod - RGB</t>
-  </si>
-  <si>
-    <t>Tripod+RGB</t>
-  </si>
-  <si>
-    <t>UB-01</t>
-  </si>
-  <si>
-    <t>UB-02</t>
-  </si>
-  <si>
-    <t>UB-03</t>
-  </si>
-  <si>
-    <t>UB-04</t>
-  </si>
-  <si>
-    <t>UB-06</t>
-  </si>
-  <si>
-    <t>USB Microphone Kit - Boomarm</t>
-  </si>
-  <si>
-    <t>USB Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>USB/XLR Dynamic Mic</t>
-  </si>
-  <si>
-    <t>USB/XLR Mic</t>
-  </si>
-  <si>
-    <t>Video Microphone</t>
-  </si>
-  <si>
-    <t>Vocal Microphone</t>
-  </si>
-  <si>
-    <t>Wired</t>
-  </si>
-  <si>
-    <t>Wired Voice Amplifier</t>
-  </si>
-  <si>
-    <t>Wireless Conference Microphone</t>
-  </si>
-  <si>
-    <t>Wireless Lapel Microphone</t>
-  </si>
-  <si>
-    <t>Wireless Mic with Charging Case</t>
-  </si>
-  <si>
-    <t>Wireless Voice Amplifier</t>
-  </si>
-  <si>
-    <t>XLR Dynamic Mic</t>
-  </si>
-  <si>
-    <t>XLR Microphone Kit - Boomarm</t>
-  </si>
-  <si>
-    <t>XLR Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>#N/A</t>
   </si>
   <si>
     <t xml:space="preserve">Sep Goal </t>
@@ -2146,7 +1834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2171,6 +1859,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2561,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -2584,7 +2273,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -2607,7 +2296,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
@@ -2630,7 +2319,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>14</v>
@@ -2653,7 +2342,7 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>21</v>
@@ -2699,7 +2388,7 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>34</v>
@@ -2745,7 +2434,7 @@
         <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>78</v>
@@ -2768,7 +2457,7 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
@@ -2791,7 +2480,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>23</v>
@@ -2837,7 +2526,7 @@
         <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>660</v>
+        <v>556</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>104</v>
@@ -2860,7 +2549,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>661</v>
+        <v>557</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
@@ -2883,7 +2572,7 @@
         <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>660</v>
+        <v>556</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>123</v>
@@ -2929,7 +2618,7 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>68</v>
@@ -2952,7 +2641,7 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2975,7 +2664,7 @@
         <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>121</v>
@@ -2998,7 +2687,7 @@
         <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>86</v>
@@ -3021,7 +2710,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>27</v>
@@ -3044,7 +2733,7 @@
         <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>62</v>
@@ -3067,7 +2756,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>40</v>
@@ -3136,7 +2825,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>38</v>
@@ -3159,7 +2848,7 @@
         <v>175</v>
       </c>
       <c r="B29" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>129</v>
@@ -3228,7 +2917,7 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>44</v>
@@ -3297,7 +2986,7 @@
         <v>290</v>
       </c>
       <c r="B35" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>291</v>
@@ -3343,7 +3032,7 @@
         <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>102</v>
@@ -3389,7 +3078,7 @@
         <v>230</v>
       </c>
       <c r="B39" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>231</v>
@@ -3412,7 +3101,7 @@
         <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>142</v>
@@ -3435,7 +3124,7 @@
         <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>193</v>
@@ -3481,7 +3170,7 @@
         <v>147</v>
       </c>
       <c r="B43" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>148</v>
@@ -3504,7 +3193,7 @@
         <v>109</v>
       </c>
       <c r="B44" t="s">
-        <v>661</v>
+        <v>557</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>110</v>
@@ -3573,7 +3262,7 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>55</v>
@@ -3596,7 +3285,7 @@
         <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>14</v>
@@ -3619,7 +3308,7 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>664</v>
+        <v>560</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>90</v>
@@ -3642,7 +3331,7 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>53</v>
@@ -3665,7 +3354,7 @@
         <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>84</v>
@@ -3688,7 +3377,7 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>66</v>
@@ -3711,7 +3400,7 @@
         <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>82</v>
@@ -3757,7 +3446,7 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>129</v>
@@ -3780,7 +3469,7 @@
         <v>186</v>
       </c>
       <c r="B56" t="s">
-        <v>664</v>
+        <v>560</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>187</v>
@@ -3826,7 +3515,7 @@
         <v>139</v>
       </c>
       <c r="B58" t="s">
-        <v>664</v>
+        <v>560</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>140</v>
@@ -3918,7 +3607,7 @@
         <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>214</v>
@@ -3941,7 +3630,7 @@
         <v>130</v>
       </c>
       <c r="B63" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>131</v>
@@ -3964,7 +3653,7 @@
         <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>115</v>
@@ -3987,7 +3676,7 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>189</v>
@@ -4010,7 +3699,7 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>664</v>
+        <v>560</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>74</v>
@@ -4033,7 +3722,7 @@
         <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>134</v>
@@ -4056,7 +3745,7 @@
         <v>137</v>
       </c>
       <c r="B68" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>138</v>
@@ -4079,7 +3768,7 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>666</v>
+        <v>562</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>76</v>
@@ -4102,7 +3791,7 @@
         <v>143</v>
       </c>
       <c r="B70" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>144</v>
@@ -4148,7 +3837,7 @@
         <v>135</v>
       </c>
       <c r="B72" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>136</v>
@@ -4171,7 +3860,7 @@
         <v>190</v>
       </c>
       <c r="B73" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>191</v>
@@ -4217,7 +3906,7 @@
         <v>180</v>
       </c>
       <c r="B75" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>181</v>
@@ -4263,7 +3952,7 @@
         <v>151</v>
       </c>
       <c r="B77" t="s">
-        <v>667</v>
+        <v>563</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>152</v>
@@ -4286,7 +3975,7 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>174</v>
@@ -4309,7 +3998,7 @@
         <v>196</v>
       </c>
       <c r="B79" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>197</v>
@@ -4355,7 +4044,7 @@
         <v>167</v>
       </c>
       <c r="B81" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>168</v>
@@ -4378,7 +4067,7 @@
         <v>132</v>
       </c>
       <c r="B82" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>131</v>
@@ -4424,7 +4113,7 @@
         <v>202</v>
       </c>
       <c r="B84" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>203</v>
@@ -4447,7 +4136,7 @@
         <v>200</v>
       </c>
       <c r="B85" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>201</v>
@@ -4516,7 +4205,7 @@
         <v>208</v>
       </c>
       <c r="B88" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>209</v>
@@ -4562,7 +4251,7 @@
         <v>127</v>
       </c>
       <c r="B90" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>12</v>
@@ -4585,7 +4274,7 @@
         <v>258</v>
       </c>
       <c r="B91" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>259</v>
@@ -4608,7 +4297,7 @@
         <v>238</v>
       </c>
       <c r="B92" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>239</v>
@@ -4631,7 +4320,7 @@
         <v>219</v>
       </c>
       <c r="B93" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>220</v>
@@ -4654,7 +4343,7 @@
         <v>165</v>
       </c>
       <c r="B94" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>166</v>
@@ -4677,7 +4366,7 @@
         <v>242</v>
       </c>
       <c r="B95" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>243</v>
@@ -4700,7 +4389,7 @@
         <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>154</v>
@@ -4746,7 +4435,7 @@
         <v>176</v>
       </c>
       <c r="B98" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>177</v>
@@ -4815,7 +4504,7 @@
         <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>205</v>
@@ -4930,7 +4619,7 @@
         <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>172</v>
@@ -4976,7 +4665,7 @@
         <v>228</v>
       </c>
       <c r="B108" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>229</v>
@@ -4999,7 +4688,7 @@
         <v>248</v>
       </c>
       <c r="B109" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>249</v>
@@ -5045,7 +4734,7 @@
         <v>198</v>
       </c>
       <c r="B111" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>199</v>
@@ -5183,7 +4872,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>117</v>
@@ -5229,7 +4918,7 @@
         <v>236</v>
       </c>
       <c r="B119" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>237</v>
@@ -5321,7 +5010,7 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>21</v>
@@ -5344,7 +5033,7 @@
         <v>277</v>
       </c>
       <c r="B124" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>278</v>
@@ -5390,7 +5079,7 @@
         <v>285</v>
       </c>
       <c r="B126" t="s">
-        <v>666</v>
+        <v>562</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>286</v>
@@ -5436,7 +5125,7 @@
         <v>280</v>
       </c>
       <c r="B128" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>205</v>
@@ -5459,7 +5148,7 @@
         <v>210</v>
       </c>
       <c r="B129" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>117</v>
@@ -5505,7 +5194,7 @@
         <v>279</v>
       </c>
       <c r="B131" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>199</v>
@@ -5551,7 +5240,7 @@
         <v>194</v>
       </c>
       <c r="B133" t="s">
-        <v>658</v>
+        <v>554</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>195</v>
@@ -5597,7 +5286,7 @@
         <v>63</v>
       </c>
       <c r="B135" t="s">
-        <v>675</v>
+        <v>571</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>64</v>
@@ -5735,7 +5424,7 @@
         <v>281</v>
       </c>
       <c r="B141" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>282</v>
@@ -5758,7 +5447,7 @@
         <v>226</v>
       </c>
       <c r="B142" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>227</v>
@@ -5781,7 +5470,7 @@
         <v>292</v>
       </c>
       <c r="B143" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>293</v>
@@ -5804,7 +5493,7 @@
         <v>306</v>
       </c>
       <c r="B144" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>307</v>
@@ -5873,7 +5562,7 @@
         <v>451</v>
       </c>
       <c r="B147" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>452</v>
@@ -5896,7 +5585,7 @@
         <v>458</v>
       </c>
       <c r="B148" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>459</v>
@@ -5965,7 +5654,7 @@
         <v>456</v>
       </c>
       <c r="B151" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>457</v>
@@ -6011,7 +5700,7 @@
         <v>469</v>
       </c>
       <c r="B153" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>470</v>
@@ -6080,7 +5769,7 @@
         <v>475</v>
       </c>
       <c r="B156" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>476</v>
@@ -6149,7 +5838,7 @@
         <v>479</v>
       </c>
       <c r="B159" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>480</v>
@@ -6195,7 +5884,7 @@
         <v>483</v>
       </c>
       <c r="B161" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>484</v>
@@ -6218,7 +5907,7 @@
         <v>485</v>
       </c>
       <c r="B162" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>486</v>
@@ -6241,7 +5930,7 @@
         <v>495</v>
       </c>
       <c r="B163" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>496</v>
@@ -6264,7 +5953,7 @@
         <v>487</v>
       </c>
       <c r="B164" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>488</v>
@@ -6287,7 +5976,7 @@
         <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>492</v>
@@ -6310,7 +5999,7 @@
         <v>493</v>
       </c>
       <c r="B166" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>494</v>
@@ -6425,7 +6114,7 @@
         <v>507</v>
       </c>
       <c r="B171" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>508</v>
@@ -6494,7 +6183,7 @@
         <v>509</v>
       </c>
       <c r="B174" t="s">
-        <v>668</v>
+        <v>564</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>510</v>
@@ -6517,7 +6206,7 @@
         <v>524</v>
       </c>
       <c r="B175" t="s">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>537</v>
@@ -6540,7 +6229,7 @@
         <v>511</v>
       </c>
       <c r="B176" t="s">
-        <v>669</v>
+        <v>565</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>512</v>
@@ -6563,7 +6252,7 @@
         <v>513</v>
       </c>
       <c r="B177" t="s">
-        <v>669</v>
+        <v>565</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>514</v>
@@ -6586,7 +6275,7 @@
         <v>513</v>
       </c>
       <c r="B178" t="s">
-        <v>669</v>
+        <v>565</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>514</v>
@@ -6632,7 +6321,7 @@
         <v>163</v>
       </c>
       <c r="B180" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>164</v>
@@ -6655,7 +6344,7 @@
         <v>300</v>
       </c>
       <c r="B181" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>301</v>
@@ -6678,7 +6367,7 @@
         <v>314</v>
       </c>
       <c r="B182" t="s">
-        <v>670</v>
+        <v>566</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>315</v>
@@ -6701,7 +6390,7 @@
         <v>308</v>
       </c>
       <c r="B183" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>309</v>
@@ -6724,7 +6413,7 @@
         <v>316</v>
       </c>
       <c r="B184" t="s">
-        <v>670</v>
+        <v>566</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>317</v>
@@ -6747,7 +6436,7 @@
         <v>384</v>
       </c>
       <c r="B185" t="s">
-        <v>671</v>
+        <v>567</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>385</v>
@@ -6793,7 +6482,7 @@
         <v>372</v>
       </c>
       <c r="B187" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>373</v>
@@ -6816,7 +6505,7 @@
         <v>408</v>
       </c>
       <c r="B188" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>409</v>
@@ -6839,7 +6528,7 @@
         <v>298</v>
       </c>
       <c r="B189" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>299</v>
@@ -6885,7 +6574,7 @@
         <v>340</v>
       </c>
       <c r="B191" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>341</v>
@@ -6908,7 +6597,7 @@
         <v>354</v>
       </c>
       <c r="B192" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>355</v>
@@ -6931,7 +6620,7 @@
         <v>338</v>
       </c>
       <c r="B193" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>339</v>
@@ -6954,7 +6643,7 @@
         <v>362</v>
       </c>
       <c r="B194" t="s">
-        <v>667</v>
+        <v>563</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>363</v>
@@ -6977,7 +6666,7 @@
         <v>344</v>
       </c>
       <c r="B195" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>345</v>
@@ -7023,7 +6712,7 @@
         <v>221</v>
       </c>
       <c r="B197" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>222</v>
@@ -7069,7 +6758,7 @@
         <v>342</v>
       </c>
       <c r="B199" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>343</v>
@@ -7092,7 +6781,7 @@
         <v>326</v>
       </c>
       <c r="B200" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>327</v>
@@ -7115,7 +6804,7 @@
         <v>318</v>
       </c>
       <c r="B201" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>319</v>
@@ -7138,7 +6827,7 @@
         <v>244</v>
       </c>
       <c r="B202" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>245</v>
@@ -7161,7 +6850,7 @@
         <v>296</v>
       </c>
       <c r="B203" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>297</v>
@@ -7207,7 +6896,7 @@
         <v>332</v>
       </c>
       <c r="B205" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>333</v>
@@ -7230,7 +6919,7 @@
         <v>304</v>
       </c>
       <c r="B206" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>305</v>
@@ -7253,7 +6942,7 @@
         <v>266</v>
       </c>
       <c r="B207" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>227</v>
@@ -7276,7 +6965,7 @@
         <v>322</v>
       </c>
       <c r="B208" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>323</v>
@@ -7299,7 +6988,7 @@
         <v>334</v>
       </c>
       <c r="B209" t="s">
-        <v>670</v>
+        <v>566</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>335</v>
@@ -7322,7 +7011,7 @@
         <v>289</v>
       </c>
       <c r="B210" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>243</v>
@@ -7345,7 +7034,7 @@
         <v>336</v>
       </c>
       <c r="B211" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>337</v>
@@ -7368,7 +7057,7 @@
         <v>346</v>
       </c>
       <c r="B212" t="s">
-        <v>673</v>
+        <v>569</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>347</v>
@@ -7391,7 +7080,7 @@
         <v>320</v>
       </c>
       <c r="B213" t="s">
-        <v>671</v>
+        <v>567</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>321</v>
@@ -7437,7 +7126,7 @@
         <v>310</v>
       </c>
       <c r="B215" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>311</v>
@@ -7460,7 +7149,7 @@
         <v>294</v>
       </c>
       <c r="B216" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>295</v>
@@ -7506,7 +7195,7 @@
         <v>352</v>
       </c>
       <c r="B218" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>353</v>
@@ -7529,7 +7218,7 @@
         <v>356</v>
       </c>
       <c r="B219" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>357</v>
@@ -7552,7 +7241,7 @@
         <v>358</v>
       </c>
       <c r="B220" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>359</v>
@@ -7575,7 +7264,7 @@
         <v>360</v>
       </c>
       <c r="B221" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>361</v>
@@ -7598,7 +7287,7 @@
         <v>364</v>
       </c>
       <c r="B222" t="s">
-        <v>674</v>
+        <v>570</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>365</v>
@@ -7621,7 +7310,7 @@
         <v>366</v>
       </c>
       <c r="B223" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>367</v>
@@ -7644,7 +7333,7 @@
         <v>368</v>
       </c>
       <c r="B224" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>369</v>
@@ -7667,7 +7356,7 @@
         <v>370</v>
       </c>
       <c r="B225" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>371</v>
@@ -7690,7 +7379,7 @@
         <v>374</v>
       </c>
       <c r="B226" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>375</v>
@@ -7713,7 +7402,7 @@
         <v>376</v>
       </c>
       <c r="B227" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>377</v>
@@ -7736,7 +7425,7 @@
         <v>378</v>
       </c>
       <c r="B228" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>379</v>
@@ -7782,7 +7471,7 @@
         <v>382</v>
       </c>
       <c r="B230" t="s">
-        <v>674</v>
+        <v>570</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>383</v>
@@ -7805,7 +7494,7 @@
         <v>386</v>
       </c>
       <c r="B231" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>387</v>
@@ -7828,7 +7517,7 @@
         <v>388</v>
       </c>
       <c r="B232" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>389</v>
@@ -7851,7 +7540,7 @@
         <v>390</v>
       </c>
       <c r="B233" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>391</v>
@@ -7874,7 +7563,7 @@
         <v>392</v>
       </c>
       <c r="B234" t="s">
-        <v>667</v>
+        <v>563</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>393</v>
@@ -7897,7 +7586,7 @@
         <v>394</v>
       </c>
       <c r="B235" t="s">
-        <v>674</v>
+        <v>570</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>395</v>
@@ -7920,7 +7609,7 @@
         <v>396</v>
       </c>
       <c r="B236" t="s">
-        <v>671</v>
+        <v>567</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>397</v>
@@ -7943,7 +7632,7 @@
         <v>398</v>
       </c>
       <c r="B237" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>399</v>
@@ -7966,7 +7655,7 @@
         <v>400</v>
       </c>
       <c r="B238" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>401</v>
@@ -7989,7 +7678,7 @@
         <v>402</v>
       </c>
       <c r="B239" t="s">
-        <v>672</v>
+        <v>568</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>403</v>
@@ -8012,7 +7701,7 @@
         <v>404</v>
       </c>
       <c r="B240" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>405</v>
@@ -8058,7 +7747,7 @@
         <v>410</v>
       </c>
       <c r="B242" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>411</v>
@@ -8081,7 +7770,7 @@
         <v>412</v>
       </c>
       <c r="B243" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>413</v>
@@ -8104,7 +7793,7 @@
         <v>414</v>
       </c>
       <c r="B244" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>415</v>
@@ -8127,7 +7816,7 @@
         <v>416</v>
       </c>
       <c r="B245" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>417</v>
@@ -8150,7 +7839,7 @@
         <v>418</v>
       </c>
       <c r="B246" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>419</v>
@@ -8173,7 +7862,7 @@
         <v>420</v>
       </c>
       <c r="B247" t="s">
-        <v>663</v>
+        <v>559</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>421</v>
@@ -8357,7 +8046,7 @@
         <v>436</v>
       </c>
       <c r="B255" t="s">
-        <v>670</v>
+        <v>566</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>437</v>
@@ -8380,7 +8069,7 @@
         <v>438</v>
       </c>
       <c r="B256" t="s">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>439</v>
@@ -8403,7 +8092,7 @@
         <v>440</v>
       </c>
       <c r="B257" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>441</v>
@@ -8426,7 +8115,7 @@
         <v>442</v>
       </c>
       <c r="B258" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>443</v>
@@ -8449,7 +8138,7 @@
         <v>444</v>
       </c>
       <c r="B259" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>445</v>
@@ -8472,7 +8161,7 @@
         <v>446</v>
       </c>
       <c r="B260" t="s">
-        <v>659</v>
+        <v>555</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>447</v>
@@ -8495,7 +8184,7 @@
         <v>525</v>
       </c>
       <c r="B261" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>538</v>
@@ -8518,7 +8207,7 @@
         <v>526</v>
       </c>
       <c r="B262" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>539</v>
@@ -8541,7 +8230,7 @@
         <v>527</v>
       </c>
       <c r="B263" t="s">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>540</v>
@@ -8564,7 +8253,7 @@
         <v>528</v>
       </c>
       <c r="B264" t="s">
-        <v>671</v>
+        <v>567</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>541</v>
@@ -8587,7 +8276,7 @@
         <v>529</v>
       </c>
       <c r="B265" t="s">
-        <v>676</v>
+        <v>572</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>542</v>
@@ -8777,7 +8466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB80F62C-1212-4C77-B22D-E2230B23F9F4}">
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.88671875" customWidth="1"/>
@@ -8794,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>654</v>
+        <v>550</v>
       </c>
       <c r="D1" t="s">
         <v>520</v>
@@ -8805,1939 +8494,511 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="C2">
-        <v>369389.83050847455</v>
-      </c>
-      <c r="D2">
-        <v>12312.994350282486</v>
-      </c>
-      <c r="E2">
-        <v>120</v>
+        <v>463</v>
+      </c>
+      <c r="C2" s="5">
+        <v>67516.101694915254</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2250.536723163842</v>
+      </c>
+      <c r="E2" s="10">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C3">
-        <v>741419.49152542371</v>
-      </c>
-      <c r="D3">
-        <v>24713.983050847459</v>
-      </c>
-      <c r="E3">
-        <v>125</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3196610.1694915253</v>
+      </c>
+      <c r="D3" s="5">
+        <v>106553.67231638417</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="C4">
-        <v>508423.72881355934</v>
-      </c>
-      <c r="D4">
-        <v>16947.457627118645</v>
-      </c>
-      <c r="E4">
-        <v>60</v>
+        <v>555</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3844483.0508474568</v>
+      </c>
+      <c r="D4" s="5">
+        <v>128149.43502824858</v>
+      </c>
+      <c r="E4" s="10">
+        <v>910</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="C5">
-        <v>45757.627118644072</v>
-      </c>
-      <c r="D5">
-        <v>1525.2542372881358</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
+        <v>571</v>
+      </c>
+      <c r="C5" s="5">
+        <v>18472.881355932204</v>
+      </c>
+      <c r="D5" s="5">
+        <v>615.76271186440681</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2356688.1355932201</v>
+      </c>
+      <c r="D6" s="5">
+        <v>78556.271186440674</v>
+      </c>
+      <c r="E6" s="10">
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>564</v>
+      </c>
+      <c r="C7" s="5">
+        <v>462511.86440677976</v>
+      </c>
+      <c r="D7" s="5">
+        <v>15417.062146892657</v>
+      </c>
+      <c r="E7" s="10">
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>454</v>
+      </c>
+      <c r="C8" s="5">
+        <v>50828.813559322036</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1694.2937853107344</v>
+      </c>
+      <c r="E8" s="10">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1453360.1694915255</v>
+      </c>
+      <c r="D9" s="5">
+        <v>48445.338983050839</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1035</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="C10">
-        <v>59305.084745762717</v>
-      </c>
-      <c r="D10">
-        <v>1976.8361581920906</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
+        <v>449</v>
+      </c>
+      <c r="C10" s="5">
+        <v>663224.57627118647</v>
+      </c>
+      <c r="D10" s="5">
+        <v>22107.485875706214</v>
+      </c>
+      <c r="E10" s="10">
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="C11">
-        <v>59305.084745762717</v>
-      </c>
-      <c r="D11">
-        <v>1976.8361581920906</v>
-      </c>
-      <c r="E11">
-        <v>20</v>
+        <v>560</v>
+      </c>
+      <c r="C11" s="5">
+        <v>187664.40677966102</v>
+      </c>
+      <c r="D11" s="5">
+        <v>6255.480225988701</v>
+      </c>
+      <c r="E11" s="10">
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="C12">
-        <v>889512.71186440683</v>
-      </c>
-      <c r="D12">
-        <v>29650.423728813559</v>
-      </c>
-      <c r="E12">
-        <v>375</v>
+        <v>518</v>
+      </c>
+      <c r="C12" s="5">
+        <v>110114.40677966102</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3670.4802259887006</v>
+      </c>
+      <c r="E12" s="10">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="C13">
-        <v>112266.94915254238</v>
-      </c>
-      <c r="D13">
-        <v>3742.2316384180795</v>
-      </c>
-      <c r="E13">
-        <v>25</v>
+        <v>563</v>
+      </c>
+      <c r="C13" s="5">
+        <v>42368.644067796609</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1412.2881355932202</v>
+      </c>
+      <c r="E13" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="C14">
-        <v>76266.94915254238</v>
-      </c>
-      <c r="D14">
-        <v>2542.231638418079</v>
-      </c>
-      <c r="E14">
-        <v>5</v>
+        <v>565</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="C15">
-        <v>56264.406779661018</v>
-      </c>
-      <c r="D15">
-        <v>1875.4802259887006</v>
-      </c>
-      <c r="E15">
-        <v>8</v>
+        <v>559</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1284796.6101694915</v>
+      </c>
+      <c r="D15" s="5">
+        <v>42826.55367231639</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1440</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="C16">
-        <v>13980.508474576272</v>
-      </c>
-      <c r="D16">
-        <v>466.0169491525424</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
+        <v>552</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3231025.423728813</v>
+      </c>
+      <c r="D16" s="5">
+        <v>107700.84745762714</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1390</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="C17">
-        <v>55073.728813559326</v>
-      </c>
-      <c r="D17">
-        <v>1835.7909604519775</v>
-      </c>
-      <c r="E17">
-        <v>13</v>
+        <v>553</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2303728.8135593222</v>
+      </c>
+      <c r="D17" s="5">
+        <v>76790.960451977415</v>
+      </c>
+      <c r="E17" s="10">
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="C18">
-        <v>1121448.3050847459</v>
-      </c>
-      <c r="D18">
-        <v>37381.610169491527</v>
-      </c>
-      <c r="E18">
-        <v>191</v>
+        <v>50</v>
+      </c>
+      <c r="C18" s="5">
+        <v>519161.86440677964</v>
+      </c>
+      <c r="D18" s="5">
+        <v>17305.395480225987</v>
+      </c>
+      <c r="E18" s="10">
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="C19">
-        <v>1284796.6101694915</v>
-      </c>
-      <c r="D19">
-        <v>42826.55367231639</v>
-      </c>
-      <c r="E19">
-        <v>1440</v>
+        <v>568</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20">
-        <v>3196610.1694915253</v>
-      </c>
-      <c r="D20">
-        <v>106553.67231638417</v>
-      </c>
-      <c r="E20">
-        <v>1000</v>
+        <v>572</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+        <v>558</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1205241.5254237289</v>
+      </c>
+      <c r="D21" s="5">
+        <v>40174.717514124291</v>
+      </c>
+      <c r="E21" s="10">
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="C22">
-        <v>7116.1016949152545</v>
-      </c>
-      <c r="D22">
-        <v>237.20338983050848</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
+        <v>561</v>
+      </c>
+      <c r="C22" s="5">
+        <v>299658.4745762712</v>
+      </c>
+      <c r="D22" s="5">
+        <v>9988.6158192090406</v>
+      </c>
+      <c r="E22" s="10">
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
+        <v>554</v>
+      </c>
+      <c r="C23" s="5">
+        <v>3537703.3898305087</v>
+      </c>
+      <c r="D23" s="5">
+        <v>117923.44632768363</v>
+      </c>
+      <c r="E23" s="10">
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="C24">
-        <v>137665.25423728814</v>
-      </c>
-      <c r="D24">
-        <v>4588.8418079096045</v>
-      </c>
-      <c r="E24">
-        <v>55</v>
+        <v>557</v>
+      </c>
+      <c r="C24" s="5">
+        <v>496478.81355932204</v>
+      </c>
+      <c r="D24" s="5">
+        <v>16549.293785310736</v>
+      </c>
+      <c r="E24" s="10">
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
+        <v>569</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
+        <v>570</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="C27" s="5">
+        <v>203220.33898305087</v>
+      </c>
+      <c r="D27" s="5">
+        <v>6774.0112994350293</v>
+      </c>
+      <c r="E27" s="10">
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="C28">
-        <v>222394.06779661018</v>
-      </c>
-      <c r="D28">
-        <v>7413.1355932203396</v>
-      </c>
-      <c r="E28">
-        <v>75</v>
+        <v>562</v>
+      </c>
+      <c r="C28" s="5">
+        <v>58052.542372881362</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1935.0847457627119</v>
+      </c>
+      <c r="E28" s="10">
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C29">
-        <v>473559.32203389832</v>
-      </c>
-      <c r="D29">
-        <v>15785.310734463277</v>
-      </c>
-      <c r="E29">
-        <v>200</v>
+        <v>556</v>
+      </c>
+      <c r="C29" s="5">
+        <v>910381.35593220335</v>
+      </c>
+      <c r="D29" s="5">
+        <v>30346.045197740117</v>
+      </c>
+      <c r="E29" s="10">
+        <v>750</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
+        <v>566</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31">
-        <v>1453360.1694915255</v>
-      </c>
-      <c r="D31">
-        <v>48445.338983050839</v>
-      </c>
-      <c r="E31">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>655</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>655</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="C33">
-        <v>23300.847457627118</v>
-      </c>
-      <c r="D33">
-        <v>776.69491525423723</v>
-      </c>
-      <c r="E33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>655</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="C34">
-        <v>203364.40677966102</v>
-      </c>
-      <c r="D34">
-        <v>6778.8135593220341</v>
-      </c>
-      <c r="E34">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>655</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C35">
-        <v>74347.457627118652</v>
-      </c>
-      <c r="D35">
-        <v>2478.2485875706216</v>
-      </c>
-      <c r="E35">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>655</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="C36">
-        <v>22453.389830508477</v>
-      </c>
-      <c r="D36">
-        <v>748.44632768361589</v>
-      </c>
-      <c r="E36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>655</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="C37">
-        <v>97855.932203389835</v>
-      </c>
-      <c r="D37">
-        <v>3261.8644067796613</v>
-      </c>
-      <c r="E37">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>655</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="C38">
-        <v>600444.91525423736</v>
-      </c>
-      <c r="D38">
-        <v>20014.830508474577</v>
-      </c>
-      <c r="E38">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>655</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="C39">
-        <v>16014.406779661018</v>
-      </c>
-      <c r="D39">
-        <v>533.81355932203394</v>
-      </c>
-      <c r="E39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>655</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="C40">
-        <v>22877.118644067799</v>
-      </c>
-      <c r="D40">
-        <v>762.57062146892667</v>
-      </c>
-      <c r="E40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>655</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="C42">
-        <v>402330.50847457629</v>
-      </c>
-      <c r="D42">
-        <v>13411.016949152543</v>
-      </c>
-      <c r="E42">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>655</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="C43">
-        <v>74542.372881355943</v>
-      </c>
-      <c r="D43">
-        <v>2484.7457627118647</v>
-      </c>
-      <c r="E43">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>655</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="C44">
-        <v>169406.77966101695</v>
-      </c>
-      <c r="D44">
-        <v>5646.8926553672318</v>
-      </c>
-      <c r="E44">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>655</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C45">
-        <v>110114.40677966102</v>
-      </c>
-      <c r="D45">
-        <v>3670.4802259887006</v>
-      </c>
-      <c r="E45">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>655</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>655</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>655</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="C48">
-        <v>42368.644067796609</v>
-      </c>
-      <c r="D48">
-        <v>1412.2881355932202</v>
-      </c>
-      <c r="E48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>655</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="C49">
-        <v>20758.474576271186</v>
-      </c>
-      <c r="D49">
-        <v>691.94915254237287</v>
-      </c>
-      <c r="E49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>655</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>655</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>655</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="C52">
-        <v>5336.4406779661022</v>
-      </c>
-      <c r="D52">
-        <v>177.88135593220341</v>
-      </c>
-      <c r="E52">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>655</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>655</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C54">
-        <v>269421.18644067802</v>
-      </c>
-      <c r="D54">
-        <v>8980.7062146892658</v>
-      </c>
-      <c r="E54">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>655</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="C55">
-        <v>55063.5593220339</v>
-      </c>
-      <c r="D55">
-        <v>1835.4519774011301</v>
-      </c>
-      <c r="E55">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>655</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C56">
-        <v>58052.542372881362</v>
-      </c>
-      <c r="D56">
-        <v>1935.0847457627119</v>
-      </c>
-      <c r="E56">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>655</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>655</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="C58">
-        <v>496478.81355932204</v>
-      </c>
-      <c r="D58">
-        <v>16549.293785310736</v>
-      </c>
-      <c r="E58">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>655</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>655</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="C60">
+        <v>519</v>
+      </c>
+      <c r="C31" s="5">
         <v>8472.8813559322043</v>
       </c>
-      <c r="D60">
+      <c r="D31" s="5">
         <v>282.4293785310735</v>
       </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>655</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>655</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="C62">
-        <v>22878.813559322036</v>
-      </c>
-      <c r="D62">
-        <v>762.62711864406788</v>
-      </c>
-      <c r="E62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>655</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="C63">
-        <v>23387.288135593222</v>
-      </c>
-      <c r="D63">
-        <v>779.57627118644075</v>
-      </c>
-      <c r="E63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>655</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="C64">
-        <v>57199.152542372882</v>
-      </c>
-      <c r="D64">
-        <v>1906.638418079096</v>
-      </c>
-      <c r="E64">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>655</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="C65">
-        <v>34573.728813559326</v>
-      </c>
-      <c r="D65">
-        <v>1152.4576271186443</v>
-      </c>
-      <c r="E65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>655</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="C66">
-        <v>24150</v>
-      </c>
-      <c r="D66">
-        <v>805</v>
-      </c>
-      <c r="E66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>655</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="C67">
-        <v>39402.542372881355</v>
-      </c>
-      <c r="D67">
-        <v>1313.4180790960452</v>
-      </c>
-      <c r="E67">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>655</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="C68">
-        <v>13811.864406779661</v>
-      </c>
-      <c r="D68">
-        <v>460.39548022598871</v>
-      </c>
-      <c r="E68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>655</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>655</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="C70">
-        <v>29656.77966101695</v>
-      </c>
-      <c r="D70">
-        <v>988.5593220338983</v>
-      </c>
-      <c r="E70">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>655</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="C71">
-        <v>381317.79661016952</v>
-      </c>
-      <c r="D71">
-        <v>12710.593220338984</v>
-      </c>
-      <c r="E71">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>655</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="C72">
-        <v>27538.135593220341</v>
-      </c>
-      <c r="D72">
-        <v>917.93785310734472</v>
-      </c>
-      <c r="E72">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>655</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="C73">
-        <v>175408.4745762712</v>
-      </c>
-      <c r="D73">
-        <v>5846.9491525423737</v>
-      </c>
-      <c r="E73">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>655</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="C74">
-        <v>22029.661016949154</v>
-      </c>
-      <c r="D74">
-        <v>734.32203389830511</v>
-      </c>
-      <c r="E74">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>655</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="C75">
-        <v>58461.864406779663</v>
-      </c>
-      <c r="D75">
-        <v>1948.7288135593221</v>
-      </c>
-      <c r="E75">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>655</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="C76">
-        <v>169474.57627118644</v>
-      </c>
-      <c r="D76">
-        <v>5649.1525423728808</v>
-      </c>
-      <c r="E76">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>655</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="C77">
-        <v>21353.389830508477</v>
-      </c>
-      <c r="D77">
-        <v>711.77966101694926</v>
-      </c>
-      <c r="E77">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>655</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="C78">
-        <v>42705.084745762717</v>
-      </c>
-      <c r="D78">
-        <v>1423.5028248587573</v>
-      </c>
-      <c r="E78">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>655</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="C79">
-        <v>11862.71186440678</v>
-      </c>
-      <c r="D79">
-        <v>395.42372881355931</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>655</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>655</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>655</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C82">
-        <v>18642.372881355932</v>
-      </c>
-      <c r="D82">
-        <v>621.4124293785311</v>
-      </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>655</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>655</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>655</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="C85">
-        <v>12710.169491525425</v>
-      </c>
-      <c r="D85">
-        <v>423.67231638418082</v>
-      </c>
-      <c r="E85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>655</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C86">
-        <v>14402.542372881357</v>
-      </c>
-      <c r="D86">
-        <v>480.08474576271186</v>
-      </c>
-      <c r="E86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>655</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="C87">
-        <v>3812.71186440678</v>
-      </c>
-      <c r="D87">
-        <v>127.09039548022601</v>
-      </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>655</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C88">
-        <v>203220.33898305087</v>
-      </c>
-      <c r="D88">
-        <v>6774.0112994350293</v>
-      </c>
-      <c r="E88">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>655</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>655</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="C90">
-        <v>3461436.4406779665</v>
-      </c>
-      <c r="D90">
-        <v>115381.21468926554</v>
-      </c>
-      <c r="E90">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>655</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="C91">
-        <v>189317.79661016952</v>
-      </c>
-      <c r="D91">
-        <v>6310.5932203389839</v>
-      </c>
-      <c r="E91">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>655</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="C92">
-        <v>135528.81355932204</v>
-      </c>
-      <c r="D92">
-        <v>4517.6271186440681</v>
-      </c>
-      <c r="E92">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>655</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>655</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="C94">
-        <v>88978.813559322036</v>
-      </c>
-      <c r="D94">
-        <v>2965.9604519774011</v>
-      </c>
-      <c r="E94">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>655</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="C95">
-        <v>163970.33898305087</v>
-      </c>
-      <c r="D95">
-        <v>5465.6779661016953</v>
-      </c>
-      <c r="E95">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>655</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="C96">
-        <v>108466.10169491525</v>
-      </c>
-      <c r="D96">
-        <v>3615.536723163842</v>
-      </c>
-      <c r="E96">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>655</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="C97">
-        <v>32201.69491525424</v>
-      </c>
-      <c r="D97">
-        <v>1073.3898305084747</v>
-      </c>
-      <c r="E97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>655</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="C98">
-        <v>27455.084745762713</v>
-      </c>
-      <c r="D98">
-        <v>915.16949152542372</v>
-      </c>
-      <c r="E98">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>655</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C99">
-        <v>2572779.661016949</v>
-      </c>
-      <c r="D99">
-        <v>85759.322033898308</v>
-      </c>
-      <c r="E99">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>655</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="C100">
-        <v>29644.067796610172</v>
-      </c>
-      <c r="D100">
-        <v>988.13559322033916</v>
-      </c>
-      <c r="E100">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>655</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="C101">
-        <v>38974.576271186445</v>
-      </c>
-      <c r="D101">
-        <v>1299.1525423728815</v>
-      </c>
-      <c r="E101">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>655</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="C102">
-        <v>16944.91525423729</v>
-      </c>
-      <c r="D102">
-        <v>564.83050847457639</v>
-      </c>
-      <c r="E102">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>655</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>655</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="C104">
-        <v>99310.169491525434</v>
-      </c>
-      <c r="D104">
-        <v>3310.3389830508477</v>
-      </c>
-      <c r="E104">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>655</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="C105">
-        <v>50828.813559322036</v>
-      </c>
-      <c r="D105">
-        <v>1694.2937853107344</v>
-      </c>
-      <c r="E105">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>655</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="C106">
-        <v>508050.84745762713</v>
-      </c>
-      <c r="D106">
-        <v>16935.028248587572</v>
-      </c>
-      <c r="E106">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>655</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="C107">
-        <v>1830169.4915254237</v>
-      </c>
-      <c r="D107">
-        <v>61005.649717514127</v>
-      </c>
-      <c r="E107">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>655</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="C108">
-        <v>299658.4745762712</v>
-      </c>
-      <c r="D108">
-        <v>9988.6158192090406</v>
-      </c>
-      <c r="E108">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>655</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="C109">
-        <v>0</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>655</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="C110">
-        <v>929008.47457627126</v>
-      </c>
-      <c r="D110">
-        <v>30966.949152542369</v>
-      </c>
-      <c r="E110">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>655</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="C111">
-        <v>402330.50847457629</v>
-      </c>
-      <c r="D111">
-        <v>13411.016949152543</v>
-      </c>
-      <c r="E111">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>655</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="C112">
-        <v>37108.47457627119</v>
-      </c>
-      <c r="D112">
-        <v>1236.949152542373</v>
-      </c>
-      <c r="E112">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>655</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="C113">
-        <v>352004.23728813563</v>
-      </c>
-      <c r="D113">
-        <v>11733.474576271186</v>
-      </c>
-      <c r="E113">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>655</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="C114">
-        <v>54203.38983050848</v>
-      </c>
-      <c r="D114">
-        <v>1806.7796610169494</v>
-      </c>
-      <c r="E114">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>655</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="C115">
-        <v>18472.881355932204</v>
-      </c>
-      <c r="D115">
-        <v>615.76271186440681</v>
-      </c>
-      <c r="E115">
+      <c r="E31" s="10">
         <v>2</v>
       </c>
     </row>
